--- a/ssp_modeling/transformations_ndc/templates/calibrated/morocco/model_input_variables_morocco_se_calibrated.xlsx
+++ b/ssp_modeling/transformations_ndc/templates/calibrated/morocco/model_input_variables_morocco_se_calibrated.xlsx
@@ -847,145 +847,145 @@
         <v>316.7154648</v>
       </c>
       <c r="S2">
-        <v>326.67616616796</v>
+        <v>326.6761662</v>
       </c>
       <c r="T2">
-        <v>337.4630131748261</v>
+        <v>337.4630132</v>
       </c>
       <c r="U2">
-        <v>348.8760122803987</v>
+        <v>348.8760123</v>
       </c>
       <c r="V2">
-        <v>360.7203528973182</v>
+        <v>360.7203529</v>
       </c>
       <c r="W2">
-        <v>372.9090936217186</v>
+        <v>372.9090936</v>
       </c>
       <c r="X2">
-        <v>385.6215646232829</v>
+        <v>385.6215646</v>
       </c>
       <c r="Y2">
-        <v>398.6240226522625</v>
+        <v>398.6240227</v>
       </c>
       <c r="Z2">
-        <v>411.9166842658149</v>
+        <v>411.9166843</v>
       </c>
       <c r="AA2">
-        <v>425.4994496946236</v>
+        <v>425.4994497</v>
       </c>
       <c r="AB2">
-        <v>439.3718922077129</v>
+        <v>439.3718922</v>
       </c>
       <c r="AC2">
-        <v>453.5332477225603</v>
+        <v>453.5332477</v>
       </c>
       <c r="AD2">
-        <v>467.9824046920487</v>
+        <v>467.9824047</v>
       </c>
       <c r="AE2">
-        <v>482.7178943001522</v>
+        <v>482.7178943</v>
       </c>
       <c r="AF2">
-        <v>497.7378809985261</v>
+        <v>497.737881</v>
       </c>
       <c r="AG2">
-        <v>513.0401534163518</v>
+        <v>513.0401534</v>
       </c>
       <c r="AH2">
-        <v>528.6221156758853</v>
+        <v>528.6221157</v>
       </c>
       <c r="AI2">
-        <v>544.4807791461619</v>
+        <v>544.4807790999999</v>
       </c>
       <c r="AJ2">
-        <v>560.8152025205468</v>
+        <v>560.8152025000001</v>
       </c>
       <c r="AK2">
-        <v>577.6396585961633</v>
+        <v>577.6396586</v>
       </c>
       <c r="AL2">
-        <v>594.9688483540482</v>
+        <v>594.9688484</v>
       </c>
       <c r="AM2">
-        <v>612.8179138046696</v>
+        <v>612.8179138</v>
       </c>
       <c r="AN2">
-        <v>631.2024512188098</v>
+        <v>631.2024512</v>
       </c>
       <c r="AO2">
-        <v>650.1385247553741</v>
+        <v>650.1385248</v>
       </c>
       <c r="AP2">
-        <v>669.6426804980354</v>
+        <v>669.6426805</v>
       </c>
       <c r="AQ2">
-        <v>689.7319609129764</v>
+        <v>689.7319609</v>
       </c>
       <c r="AR2">
-        <v>710.4239197403657</v>
+        <v>710.4239197000001</v>
       </c>
       <c r="AS2">
-        <v>731.7366373325766</v>
+        <v>731.7366373</v>
       </c>
       <c r="AT2">
-        <v>753.6887364525539</v>
+        <v>753.6887365</v>
       </c>
       <c r="AU2">
-        <v>776.2993985461305</v>
+        <v>776.2993985000001</v>
       </c>
       <c r="AV2">
-        <v>799.3987902651187</v>
+        <v>799.3987903</v>
       </c>
       <c r="AW2">
-        <v>822.5929535108869</v>
+        <v>822.5929535</v>
       </c>
       <c r="AX2">
-        <v>845.7668704981745</v>
+        <v>845.7668705</v>
       </c>
       <c r="AY2">
-        <v>868.9007621649652</v>
+        <v>868.9007622</v>
       </c>
       <c r="AZ2">
-        <v>892.0950028125003</v>
+        <v>892.0950028</v>
       </c>
       <c r="BA2">
-        <v>915.5664208286682</v>
+        <v>915.5664207999999</v>
       </c>
       <c r="BB2">
-        <v>939.4943644957076</v>
+        <v>939.4943645</v>
       </c>
       <c r="BC2">
-        <v>964.0768962261384</v>
+        <v>964.0768962</v>
       </c>
       <c r="BD2">
-        <v>989.3880917195766</v>
+        <v>989.3880917</v>
       </c>
       <c r="BE2">
-        <v>1015.161907507781</v>
+        <v>1015.161908</v>
       </c>
       <c r="BF2">
-        <v>1041.0752356972</v>
+        <v>1041.075236</v>
       </c>
       <c r="BG2">
-        <v>1066.846219105143</v>
+        <v>1066.846219</v>
       </c>
       <c r="BH2">
-        <v>1092.209006584846</v>
+        <v>1092.209007</v>
       </c>
       <c r="BI2">
-        <v>1116.910928066223</v>
+        <v>1116.910928</v>
       </c>
       <c r="BJ2">
-        <v>1141.149673270519</v>
+        <v>1141.149673</v>
       </c>
       <c r="BK2">
-        <v>1165.28889045616</v>
+        <v>1165.28889</v>
       </c>
       <c r="BL2">
-        <v>1189.731370330335</v>
+        <v>1189.73137</v>
       </c>
       <c r="BM2">
-        <v>1214.819430853729</v>
+        <v>1214.819431</v>
       </c>
     </row>
     <row r="3" spans="1:65">
@@ -2458,172 +2458,172 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>13620953.99095196</v>
+        <v>13620953.99</v>
       </c>
       <c r="K11">
-        <v>13671138.28154934</v>
+        <v>13671138.28</v>
       </c>
       <c r="L11">
-        <v>13726223.37011497</v>
+        <v>13726223.37</v>
       </c>
       <c r="M11">
-        <v>13773369.47951868</v>
+        <v>13773369.48</v>
       </c>
       <c r="N11">
-        <v>13816976.04649106</v>
+        <v>13816976.05</v>
       </c>
       <c r="O11">
-        <v>13867850.023025</v>
+        <v>13867850.02</v>
       </c>
       <c r="P11">
-        <v>13925421.29392466</v>
+        <v>13925421.29</v>
       </c>
       <c r="Q11">
-        <v>13993976.67988882</v>
+        <v>13993976.68</v>
       </c>
       <c r="R11">
-        <v>9695151.066504393</v>
+        <v>9695151.067</v>
       </c>
       <c r="S11">
-        <v>9534892.669750135</v>
+        <v>9534892.67</v>
       </c>
       <c r="T11">
-        <v>9370855.721642662</v>
+        <v>9370855.721999999</v>
       </c>
       <c r="U11">
-        <v>9203176.451641174</v>
+        <v>9203176.452</v>
       </c>
       <c r="V11">
-        <v>9031678.781851765</v>
+        <v>9031678.782</v>
       </c>
       <c r="W11">
-        <v>8856321.289933871</v>
+        <v>8856321.289999999</v>
       </c>
       <c r="X11">
-        <v>8677087.525182402</v>
+        <v>8677087.525</v>
       </c>
       <c r="Y11">
-        <v>8493987.514657961</v>
+        <v>8493987.515000001</v>
       </c>
       <c r="Z11">
-        <v>8307055.441236157</v>
+        <v>8307055.441</v>
       </c>
       <c r="AA11">
-        <v>8116352.088558883</v>
+        <v>8116352.089</v>
       </c>
       <c r="AB11">
-        <v>7921964.907554825</v>
+        <v>7921964.908</v>
       </c>
       <c r="AC11">
-        <v>7724000.045246531</v>
+        <v>7724000.045</v>
       </c>
       <c r="AD11">
-        <v>7522567.961208835</v>
+        <v>7522567.961</v>
       </c>
       <c r="AE11">
-        <v>7317790.918055452</v>
+        <v>7317790.918</v>
       </c>
       <c r="AF11">
-        <v>7109795.232399963</v>
+        <v>7109795.232</v>
       </c>
       <c r="AG11">
-        <v>6898700.709353909</v>
+        <v>6898700.709</v>
       </c>
       <c r="AH11">
-        <v>6684630.985874579</v>
+        <v>6684630.986</v>
       </c>
       <c r="AI11">
-        <v>6467705.818124292</v>
+        <v>6467705.818</v>
       </c>
       <c r="AJ11">
-        <v>6248044.130128529</v>
+        <v>6248044.13</v>
       </c>
       <c r="AK11">
-        <v>6025765.101954864</v>
+        <v>6025765.102</v>
       </c>
       <c r="AL11">
-        <v>5800980.075519303</v>
+        <v>5800980.076</v>
       </c>
       <c r="AM11">
-        <v>5573804.702779875</v>
+        <v>5573804.703</v>
       </c>
       <c r="AN11">
-        <v>5344347.059860674</v>
+        <v>5344347.06</v>
       </c>
       <c r="AO11">
-        <v>5112705.779450646</v>
+        <v>5112705.779</v>
       </c>
       <c r="AP11">
-        <v>4878940.797993477</v>
+        <v>4878940.798</v>
       </c>
       <c r="AQ11">
-        <v>4643119.84866587</v>
+        <v>4643119.849</v>
       </c>
       <c r="AR11">
-        <v>4405299.890794543</v>
+        <v>4405299.891</v>
       </c>
       <c r="AS11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="AT11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="AU11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="AV11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="AW11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="AX11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="AY11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="AZ11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="BA11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="BB11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="BC11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="BD11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="BE11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="BF11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="BG11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="BH11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="BI11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="BJ11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="BK11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="BL11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
       <c r="BM11">
-        <v>4165521.085336176</v>
+        <v>4165521.085</v>
       </c>
     </row>
     <row r="12" spans="1:65">
@@ -2640,172 +2640,172 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>20986634.00904803</v>
+        <v>20986634.01</v>
       </c>
       <c r="K12">
-        <v>21352318.71845066</v>
+        <v>21352318.72</v>
       </c>
       <c r="L12">
-        <v>21720168.62988503</v>
+        <v>21720168.63</v>
       </c>
       <c r="M12">
-        <v>22066390.52048131</v>
+        <v>22066390.52</v>
       </c>
       <c r="N12">
-        <v>22393921.95350894</v>
+        <v>22393921.95</v>
       </c>
       <c r="O12">
-        <v>22716357.976975</v>
+        <v>22716357.98</v>
       </c>
       <c r="P12">
-        <v>23029020.70607534</v>
+        <v>23029020.71</v>
       </c>
       <c r="Q12">
-        <v>23335087.32011118</v>
+        <v>23335087.32</v>
       </c>
       <c r="R12">
-        <v>26684402.65396238</v>
+        <v>26684402.65</v>
       </c>
       <c r="S12">
-        <v>27090815.40867548</v>
+        <v>27090815.41</v>
       </c>
       <c r="T12">
-        <v>27498084.82252509</v>
+        <v>27498084.82</v>
       </c>
       <c r="U12">
-        <v>27906406.01465388</v>
+        <v>27906406.01</v>
       </c>
       <c r="V12">
-        <v>28315028.79300047</v>
+        <v>28315028.79</v>
       </c>
       <c r="W12">
-        <v>28723542.74090282</v>
+        <v>28723542.74</v>
       </c>
       <c r="X12">
-        <v>29131572.71526379</v>
+        <v>29131572.72</v>
       </c>
       <c r="Y12">
-        <v>29538792.40172097</v>
+        <v>29538792.4</v>
       </c>
       <c r="Z12">
-        <v>29944926.63659737</v>
+        <v>29944926.64</v>
       </c>
       <c r="AA12">
-        <v>30349771.55390028</v>
+        <v>30349771.55</v>
       </c>
       <c r="AB12">
-        <v>30753209.58010083</v>
+        <v>30753209.58</v>
       </c>
       <c r="AC12">
-        <v>31155194.81337682</v>
+        <v>31155194.81</v>
       </c>
       <c r="AD12">
-        <v>31555707.16195394</v>
+        <v>31555707.16</v>
       </c>
       <c r="AE12">
-        <v>31954790.03751943</v>
+        <v>31954790.04</v>
       </c>
       <c r="AF12">
-        <v>32352527.98166092</v>
+        <v>32352527.98</v>
       </c>
       <c r="AG12">
-        <v>32749004.51681798</v>
+        <v>32749004.52</v>
       </c>
       <c r="AH12">
-        <v>33144352.04813487</v>
+        <v>33144352.05</v>
       </c>
       <c r="AI12">
-        <v>33538721.92285075</v>
+        <v>33538721.92</v>
       </c>
       <c r="AJ12">
-        <v>33932303.97359192</v>
+        <v>33932303.97</v>
       </c>
       <c r="AK12">
-        <v>34325340.49149293</v>
+        <v>34325340.49</v>
       </c>
       <c r="AL12">
-        <v>34718089.1364898</v>
+        <v>34718089.14</v>
       </c>
       <c r="AM12">
-        <v>35110901.15692724</v>
+        <v>35110901.16</v>
       </c>
       <c r="AN12">
-        <v>35504165.499584</v>
+        <v>35504165.5</v>
       </c>
       <c r="AO12">
-        <v>35898303.14662405</v>
+        <v>35898303.15</v>
       </c>
       <c r="AP12">
-        <v>36293555.38760548</v>
+        <v>36293555.39</v>
       </c>
       <c r="AQ12">
-        <v>36690291.26705405</v>
+        <v>36690291.27</v>
       </c>
       <c r="AR12">
-        <v>37088890.60334559</v>
+        <v>37088890.6</v>
       </c>
       <c r="AS12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="AT12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="AU12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="AV12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="AW12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="AX12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="AY12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="AZ12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="BA12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="BB12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="BC12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="BD12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="BE12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="BF12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="BG12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="BH12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="BI12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="BJ12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="BK12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="BL12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
       <c r="BM12">
-        <v>37489689.76802558</v>
+        <v>37489689.77</v>
       </c>
     </row>
   </sheetData>
